--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -1781,13 +1781,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>162.5</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1861,13 +1861,13 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>孙国奉</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>162.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2401,15 +2401,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -2421,7 +2417,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2439,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2557,11 +2553,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3051,13 +3051,13 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3093,13 +3093,13 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3135,13 +3135,13 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3177,15 +3177,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3197,7 +3193,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3219,11 +3215,15 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3257,13 +3257,13 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3341,15 +3341,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
@@ -3361,7 +3357,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3383,11 +3379,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3497,15 +3497,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3517,7 +3513,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3535,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3577,11 +3573,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3949,11 +3949,15 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -3965,7 +3969,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3987,15 +3991,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
@@ -4007,7 +4007,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -4907,14 +4907,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
@@ -4923,7 +4931,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4991,22 +4999,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5037,14 +5037,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
@@ -5053,7 +5061,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5075,22 +5083,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5121,20 +5121,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -5167,23 +5167,23 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -5217,22 +5217,26 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
@@ -5241,7 +5245,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5263,26 +5267,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5313,22 +5313,26 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5337,7 +5341,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5359,20 +5363,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -5405,23 +5409,23 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>17952.0</t>
+          <t>408.0</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -5455,26 +5459,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5505,22 +5505,30 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5529,7 +5537,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5551,20 +5559,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -5643,20 +5651,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -5689,22 +5697,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5713,7 +5729,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5735,30 +5751,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5767,7 +5775,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5789,20 +5797,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -5835,27 +5843,27 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
           <t>360.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>720.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -5889,20 +5897,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -5935,20 +5943,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -5981,20 +5989,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6027,30 +6035,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6081,20 +6081,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7053,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -7105,11 +7105,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7129,7 +7125,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -7167,7 +7163,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -7205,7 +7201,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -7221,7 +7217,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7239,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -7257,7 +7253,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7369,7 +7369,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7733,7 +7733,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -7847,11 +7847,15 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -7861,11 +7865,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7885,15 +7885,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -7903,7 +7899,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8277,15 +8277,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
@@ -8297,7 +8293,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8315,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8357,13 +8353,13 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr"/>
@@ -8399,11 +8395,15 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -8415,7 +8415,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8479,20 +8479,20 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -8567,20 +8567,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -8613,20 +8613,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -8701,20 +8701,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -8747,20 +8747,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
@@ -8793,20 +8793,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -9234,7 +9234,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T10:04:41.172243</t>
+          <t>生成时间: 2026-06-12T14:44:15.938850</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,10 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,6 +491,21 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>事件类型</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>增资后总股本(万股)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>认购占比</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -513,6 +531,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>设立</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>60.00%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>2016年12月，四方股份、罗永红、王金林共同出资设立星图测控有限，其中，四方股份出资1,200万元（对应持有星图测控有限60%股权）；罗永红出资400万元（对应持有星图测控有限20%股权）；王金林出资400万元（对应持有星图测控有限20%股权）。罗永红、王金林于测控有限设立时所持有的全部股权分别系为牛威和吴功友代持。</t>
         </is>
       </c>
@@ -538,6 +566,16 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>设立</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>2016年12月，四方股份、罗永红、王金林共同出资设立星图测控有限，其中，四方股份出资1,200万元（对应持有星图测控有限60%股权）；罗永红出资400万元（对应持有星图测控有限20%股权）；王金林出资400万元（对应持有星图测控有限20%股权）。罗永红、王金林于测控有限设立时所持有的全部股权分别系为牛威和吴功友代持。</t>
         </is>
       </c>
@@ -563,6 +601,16 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>设立</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>2016年12月，四方股份、罗永红、王金林共同出资设立星图测控有限，其中，四方股份出资1,200万元（对应持有星图测控有限60%股权）；罗永红出资400万元（对应持有星图测控有限20%股权）；王金林出资400万元（对应持有星图测控有限20%股权）。罗永红、王金林于测控有限设立时所持有的全部股权分别系为牛威和吴功友代持。</t>
         </is>
       </c>
@@ -588,6 +636,16 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>2017年10月9日，星图测控有限的股东会作出决议，同意：罗永红将其持有的星图测控有限20%股权转让予牛威；王金林将其持有的星图测控有限20%股权转让予吴功友。罗永红与牛威、王金林与吴功友于2017年10月9日分别签署了《股权转让协议》。本次股权转让系还原股权代持，故牛威、吴功友未向罗永红和王金林实际支付股权转让对价。星图测控有限于2017年10月25日就上述股权转让办理了工商变更登记手续。</t>
         </is>
       </c>
@@ -613,6 +671,16 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>股权转让</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>2017年10月9日，星图测控有限的股东会作出决议，同意：罗永红将其持有的星图测控有限20%股权转让予牛威；王金林将其持有的星图测控有限20%股权转让予吴功友。罗永红与牛威、王金林与吴功友于2017年10月9日分别签署了《股权转让协议》。本次股权转让系还原股权代持，故牛威、吴功友未向罗永红和王金林实际支付股权转让对价。星图测控有限于2017年10月25日就上述股权转让办理了工商变更登记手续。</t>
         </is>
       </c>
@@ -638,6 +706,16 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>46.36%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>截至本招股说明书签署日，公司总股本为82,500,000股。发行前股本结构：中科星图38,250,000股(46.36%)，策星九天23,450,781股(28.43%)，幸福一期9,174,219股(11.12%)，策星揽月4,125,000股(5.00%)，幸福二期3,000,000股(3.64%)，策星银河2,790,000股(3.38%)，策星逐日1,710,000股(2.07%)。合计82,500,000股(100.00%)。</t>
         </is>
       </c>
@@ -663,6 +741,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>28.43%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>截至本招股说明书签署日，公司总股本为82,500,000股。发行前股本结构：中科星图38,250,000股(46.36%)，策星九天23,450,781股(28.43%)，幸福一期9,174,219股(11.12%)，策星揽月4,125,000股(5.00%)，幸福二期3,000,000股(3.64%)，策星银河2,790,000股(3.38%)，策星逐日1,710,000股(2.07%)。合计82,500,000股(100.00%)。</t>
         </is>
       </c>
@@ -688,6 +776,16 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11.12%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>截至本招股说明书签署日，公司总股本为82,500,000股。发行前股本结构：中科星图38,250,000股(46.36%)，策星九天23,450,781股(28.43%)，幸福一期9,174,219股(11.12%)，策星揽月4,125,000股(5.00%)，幸福二期3,000,000股(3.64%)，策星银河2,790,000股(3.38%)，策星逐日1,710,000股(2.07%)。合计82,500,000股(100.00%)。</t>
         </is>
       </c>
@@ -713,6 +811,16 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>截至本招股说明书签署日，公司总股本为82,500,000股。发行前股本结构：中科星图38,250,000股(46.36%)，策星九天23,450,781股(28.43%)，幸福一期9,174,219股(11.12%)，策星揽月4,125,000股(5.00%)，幸福二期3,000,000股(3.64%)，策星银河2,790,000股(3.38%)，策星逐日1,710,000股(2.07%)。合计82,500,000股(100.00%)。</t>
         </is>
       </c>
@@ -738,6 +846,16 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3.64%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>截至本招股说明书签署日，公司总股本为82,500,000股。发行前股本结构：中科星图38,250,000股(46.36%)，策星九天23,450,781股(28.43%)，幸福一期9,174,219股(11.12%)，策星揽月4,125,000股(5.00%)，幸福二期3,000,000股(3.64%)，策星银河2,790,000股(3.38%)，策星逐日1,710,000股(2.07%)。合计82,500,000股(100.00%)。</t>
         </is>
       </c>
@@ -763,6 +881,16 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>截至本招股说明书签署日，公司总股本为82,500,000股。发行前股本结构：中科星图38,250,000股(46.36%)，策星九天23,450,781股(28.43%)，幸福一期9,174,219股(11.12%)，策星揽月4,125,000股(5.00%)，幸福二期3,000,000股(3.64%)，策星银河2,790,000股(3.38%)，策星逐日1,710,000股(2.07%)。合计82,500,000股(100.00%)。</t>
         </is>
       </c>
@@ -787,6 +915,16 @@
         <v>171</v>
       </c>
       <c r="G13" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，公司总股本为82,500,000股。发行前股本结构：中科星图38,250,000股(46.36%)，策星九天23,450,781股(28.43%)，幸福一期9,174,219股(11.12%)，策星揽月4,125,000股(5.00%)，幸福二期3,000,000股(3.64%)，策星银河2,790,000股(3.38%)，策星逐日1,710,000股(2.07%)。合计82,500,000股(100.00%)。</t>
         </is>
@@ -803,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -815,7 +953,10 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -866,6 +1007,21 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>快照序号</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>股东类型</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>原始创始人</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>原文证据</t>
         </is>
       </c>
@@ -901,6 +1057,21 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>2016年12月，四方股份、罗永红、王金林共同出资设立星图测控有限，其中，四方股份出资1,200万元（对应持有星图测控有限60%股权）；罗永红出资400万元（对应持有星图测控有限20%股权）；王金林出资400万元（对应持有星图测控有限20%股权）。罗永红、王金林于测控有限设立时所持有的全部股权分别系为牛威和吴功友代持。</t>
         </is>
       </c>
@@ -936,6 +1107,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>2016年12月，四方股份、罗永红、王金林共同出资设立星图测控有限，其中，四方股份出资1,200万元（对应持有星图测控有限60%股权）；罗永红出资400万元（对应持有星图测控有限20%股权）；王金林出资400万元（对应持有星图测控有限20%股权）。罗永红、王金林于测控有限设立时所持有的全部股权分别系为牛威和吴功友代持。</t>
         </is>
       </c>
@@ -971,6 +1157,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>2016年12月，四方股份、罗永红、王金林共同出资设立星图测控有限，其中，四方股份出资1,200万元（对应持有星图测控有限60%股权）；罗永红出资400万元（对应持有星图测控有限20%股权）；王金林出资400万元（对应持有星图测控有限20%股权）。罗永红、王金林于测控有限设立时所持有的全部股权分别系为牛威和吴功友代持。</t>
         </is>
       </c>
@@ -1006,6 +1207,21 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>2017年10月9日，星图测控有限的股东会作出决议，同意：罗永红将其持有的星图测控有限20%股权转让予牛威；王金林将其持有的星图测控有限20%股权转让予吴功友。罗永红与牛威、王金林与吴功友于2017年10月9日分别签署了《股权转让协议》。本次股权转让系还原股权代持，故牛威、吴功友未向罗永红和王金林实际支付股权转让对价。星图测控有限于2017年10月25日就上述股权转让办理了工商变更登记手续。</t>
         </is>
       </c>
@@ -1041,6 +1257,21 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>2017年10月9日，星图测控有限的股东会作出决议，同意：罗永红将其持有的星图测控有限20%股权转让予牛威；王金林将其持有的星图测控有限20%股权转让予吴功友。罗永红与牛威、王金林与吴功友于2017年10月9日分别签署了《股权转让协议》。本次股权转让系还原股权代持，故牛威、吴功友未向罗永红和王金林实际支付股权转让对价。星图测控有限于2017年10月25日就上述股权转让办理了工商变更登记手续。</t>
         </is>
       </c>
@@ -1076,6 +1307,21 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>截至本招股说明书签署日，公司总股本为82,500,000股。发行前股本结构：中科星图38,250,000股(46.36%)，策星九天23,450,781股(28.43%)，幸福一期9,174,219股(11.12%)，策星揽月4,125,000股(5.00%)，幸福二期3,000,000股(3.64%)，策星银河2,790,000股(3.38%)，策星逐日1,710,000股(2.07%)。合计82,500,000股(100.00%)。</t>
         </is>
       </c>
@@ -1111,6 +1357,21 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>截至本招股说明书签署日，公司总股本为82,500,000股。发行前股本结构：中科星图38,250,000股(46.36%)，策星九天23,450,781股(28.43%)，幸福一期9,174,219股(11.12%)，策星揽月4,125,000股(5.00%)，幸福二期3,000,000股(3.64%)，策星银河2,790,000股(3.38%)，策星逐日1,710,000股(2.07%)。合计82,500,000股(100.00%)。</t>
         </is>
       </c>
@@ -1146,6 +1407,21 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>截至本招股说明书签署日，公司总股本为82,500,000股。发行前股本结构：中科星图38,250,000股(46.36%)，策星九天23,450,781股(28.43%)，幸福一期9,174,219股(11.12%)，策星揽月4,125,000股(5.00%)，幸福二期3,000,000股(3.64%)，策星银河2,790,000股(3.38%)，策星逐日1,710,000股(2.07%)。合计82,500,000股(100.00%)。</t>
         </is>
       </c>
@@ -1181,6 +1457,21 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>截至本招股说明书签署日，公司总股本为82,500,000股。发行前股本结构：中科星图38,250,000股(46.36%)，策星九天23,450,781股(28.43%)，幸福一期9,174,219股(11.12%)，策星揽月4,125,000股(5.00%)，幸福二期3,000,000股(3.64%)，策星银河2,790,000股(3.38%)，策星逐日1,710,000股(2.07%)。合计82,500,000股(100.00%)。</t>
         </is>
       </c>
@@ -1216,6 +1507,21 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>截至本招股说明书签署日，公司总股本为82,500,000股。发行前股本结构：中科星图38,250,000股(46.36%)，策星九天23,450,781股(28.43%)，幸福一期9,174,219股(11.12%)，策星揽月4,125,000股(5.00%)，幸福二期3,000,000股(3.64%)，策星银河2,790,000股(3.38%)，策星逐日1,710,000股(2.07%)。合计82,500,000股(100.00%)。</t>
         </is>
       </c>
@@ -1251,6 +1557,21 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>截至本招股说明书签署日，公司总股本为82,500,000股。发行前股本结构：中科星图38,250,000股(46.36%)，策星九天23,450,781股(28.43%)，幸福一期9,174,219股(11.12%)，策星揽月4,125,000股(5.00%)，幸福二期3,000,000股(3.64%)，策星银河2,790,000股(3.38%)，策星逐日1,710,000股(2.07%)。合计82,500,000股(100.00%)。</t>
         </is>
       </c>
@@ -1285,6 +1606,21 @@
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，公司总股本为82,500,000股。发行前股本结构：中科星图38,250,000股(46.36%)，策星九天23,450,781股(28.43%)，幸福一期9,174,219股(11.12%)，策星揽月4,125,000股(5.00%)，幸福二期3,000,000股(3.64%)，策星银河2,790,000股(3.38%)，策星逐日1,710,000股(2.07%)。合计82,500,000股(100.00%)。</t>
         </is>
@@ -1301,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1475,100 +1811,84 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>evidence_text</t>
+          <t>event_context</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>str(min=20)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>source_page</t>
+          <t>post_event_total_shares</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>snapshot_date</t>
+          <t>post_event_total_capital</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>str(YYYY-MM-DD)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>snapshot_type</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>total_shares</t>
+          <t>subscription_ratio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>float|null</t>
+          <t>str|null</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1576,20 +1896,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>equity_snapshot</t>
+          <t>subscription_flow</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>total_capital</t>
+          <t>evidence_text</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>str(min=20)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1599,7 +1923,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>shareholder_name</t>
+          <t>source_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1621,15 +1945,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>shares_held</t>
+          <t>snapshot_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>str(YYYY-MM-DD)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1639,15 +1967,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>capital_contribution</t>
+          <t>snapshot_type</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>float|null</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1657,12 +1989,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>shareholding_ratio</t>
+          <t>total_shares</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>str|null</t>
+          <t>float|null</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1675,433 +2007,269 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>total_capital</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>shareholder_name</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shares_held</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>capital_contribution</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>float|null</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>shareholding_ratio</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>str|null</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>snapshot_order</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>int|null</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>shareholder_type_detail</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>is_original_founder</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>yes/no/unknown</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>equity_snapshot</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>evidence_text</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>str(min=20)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Cross-Check 结果（相邻时点股本追踪 + 认缴存量对应）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>上一时点</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>当前时点</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>股东名称</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>上一时点持股数
 (万股)</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>上一时点出资额
 (万元注册资本)</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>本次认缴/变化
 (万股)</t>
         </is>
       </c>
-      <c r="H24" s="1" t="inlineStr">
+      <c r="H32" s="1" t="inlineStr">
         <is>
           <t>预期变更后
 持股数(万股)</t>
         </is>
       </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="I32" s="1" t="inlineStr">
         <is>
           <t>PDF披露
 持股数(万股)</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>差额(万股)</t>
         </is>
       </c>
-      <c r="K24" s="1" t="inlineStr">
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="L24" s="1" t="inlineStr">
+      <c r="L32" s="1" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>孙国奉</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>175.0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>孙国敏</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>001282_三联锻造</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2004-06-18</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2014-05</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>张松满</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>162.5</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>武汉力源信息技术股份有限公司</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>深圳市云汉电子有限公司</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>301563_云汉芯城</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2008-05-07</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2014-08</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>孙国奉</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -2111,35 +2279,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -2149,35 +2317,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>301563_云汉芯城</t>
+          <t>001282_三联锻造</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2004-06-18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>162.5</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -2189,7 +2357,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2201,17 +2369,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2239,21 +2407,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2277,21 +2449,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2303,7 +2479,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2491,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2341,7 +2517,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2353,17 +2529,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>2008-05-07</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2391,17 +2567,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2417,7 +2593,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2429,17 +2605,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2467,17 +2643,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2493,7 +2669,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2505,17 +2681,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2531,7 +2707,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2543,25 +2719,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2573,7 +2745,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2585,17 +2757,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2611,7 +2783,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2623,17 +2795,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2649,7 +2821,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2661,17 +2833,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2015-12-03</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2699,17 +2871,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2737,17 +2909,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2763,7 +2935,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2775,21 +2947,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2801,7 +2977,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2989,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2851,17 +3027,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2889,17 +3065,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2915,7 +3091,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2927,17 +3103,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2965,17 +3141,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>2015-12-03</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2018-06-28</t>
-        </is>
-      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2991,7 +3167,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3189,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3029,7 +3205,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3041,25 +3217,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -3071,7 +3243,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3083,25 +3255,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
@@ -3125,25 +3293,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>1584.0</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -3155,7 +3319,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3167,17 +3331,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3205,25 +3369,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -3235,7 +3395,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3247,25 +3407,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
@@ -3277,7 +3433,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3289,25 +3445,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>2015-12-03</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>2018-06-28</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -3319,7 +3471,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3331,17 +3483,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2015-12-03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3357,7 +3509,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3369,25 +3521,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3399,7 +3547,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3411,21 +3559,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>2018-06-28</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>2020-05-28</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2020-09-23</t>
-        </is>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3437,33 +3589,37 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -3475,33 +3631,37 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>7412.0</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3513,33 +3673,37 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3551,35 +3715,35 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2012-06-12</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3600,26 +3764,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1584.0</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -3629,31 +3797,39 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3663,27 +3839,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3697,27 +3877,31 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>301581_黄山谷捷</t>
+          <t>301563_云汉芯城</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3733,7 +3917,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3745,12 +3929,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3771,7 +3955,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3783,17 +3967,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3821,17 +4005,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3859,21 +4043,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2012-06-12</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -3897,25 +4085,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -3925,11 +4109,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3939,25 +4119,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
@@ -3967,11 +4143,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3981,17 +4153,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4005,11 +4177,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4019,17 +4187,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4045,7 +4213,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4057,12 +4225,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4083,7 +4251,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4095,12 +4263,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4133,12 +4301,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4171,25 +4339,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -4199,7 +4363,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4209,21 +4377,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>2022-05-26</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4235,49 +4407,37 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>6999.972</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-0.028</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4285,49 +4445,41 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2999.988</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-0.012</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4335,49 +4487,37 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1499.994</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>-0.006</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4385,49 +4525,37 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4435,49 +4563,37 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4485,99 +4601,75 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>5000.0031</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>0.0031</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>price×shares vs amount diff=0.0%</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>3000.0012</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>0.0012</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4585,49 +4677,37 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>301581_黄山谷捷</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2022-05-26</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2912.5034</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2912.5</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>0.0034</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4635,7 +4715,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4648,34 +4728,34 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2000.0019</t>
+          <t>6999.972</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>7000.0</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>0.0019</t>
+          <t>-0.028</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -4698,34 +4778,34 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1747.5007</t>
+          <t>2999.988</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1747.5</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>0.0007</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -4748,34 +4828,34 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>1499.994</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -4803,29 +4883,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>999.9993</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-0.0007</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -4853,29 +4933,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>339.999</t>
+          <t>10000.0027</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.0027</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -4895,35 +4975,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4931,7 +5015,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4941,35 +5025,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4977,7 +5065,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -4987,27 +5075,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5015,7 +5115,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5025,35 +5125,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5061,7 +5165,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5071,27 +5175,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5099,7 +5215,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5109,35 +5225,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5145,7 +5265,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5155,39 +5275,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5195,7 +5315,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5205,39 +5325,39 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5245,7 +5365,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
@@ -5257,30 +5377,30 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -5303,36 +5423,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5341,7 +5457,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5353,32 +5469,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5387,7 +5495,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5399,36 +5507,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>罗世兵</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>204.0</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -5437,7 +5541,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5449,32 +5553,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5483,7 +5579,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5495,40 +5591,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5537,7 +5625,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5549,32 +5637,36 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5583,7 +5675,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5595,30 +5687,30 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -5641,32 +5733,36 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -5675,7 +5771,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5687,40 +5783,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5729,7 +5817,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5741,32 +5829,36 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5775,7 +5867,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5787,30 +5879,30 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -5833,37 +5925,33 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -5897,20 +5985,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -5943,20 +6031,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -5989,20 +6077,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6035,20 +6123,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -6081,20 +6169,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -6115,39 +6203,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6155,7 +6247,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6165,39 +6257,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6205,7 +6293,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6215,39 +6303,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6255,7 +6339,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6265,39 +6349,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>罗世兵 (认缴→存量)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6305,7 +6385,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6315,39 +6395,43 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6355,7 +6439,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6365,39 +6449,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6405,7 +6485,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6415,39 +6495,35 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6455,7 +6531,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6541,11 @@
           <t>603418_友升股份</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
           <t>2022-12-19</t>
@@ -6473,31 +6553,31 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6505,7 +6585,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6518,29 +6598,29 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6568,29 +6648,29 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6618,29 +6698,29 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6668,29 +6748,29 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6718,29 +6798,29 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -6768,29 +6848,29 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -6818,29 +6898,29 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -6873,24 +6953,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -6923,24 +7003,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -6962,30 +7042,42 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K145" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6993,37 +7085,49 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7031,37 +7135,49 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7069,71 +7185,99 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K148" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7141,37 +7285,49 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7179,37 +7335,49 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7217,37 +7385,49 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7255,7 +7435,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7457,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7315,7 +7495,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7353,7 +7533,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7369,7 +7549,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7571,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7414,22 +7594,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7443,31 +7623,27 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7490,22 +7666,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7521,29 +7697,29 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7559,29 +7735,29 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7597,29 +7773,29 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7642,22 +7818,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7680,22 +7856,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>688758_赛分科技</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2015-01</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7733,7 +7909,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7761,17 +7937,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7787,7 +7963,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7799,17 +7975,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -7825,7 +8001,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7837,25 +8013,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -7865,7 +8037,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7875,17 +8051,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
           <t>2015-07-09</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -7901,7 +8077,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7913,17 +8089,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -7951,17 +8127,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -7977,7 +8153,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7989,17 +8165,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8015,7 +8191,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8027,17 +8203,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8065,21 +8241,25 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
           <t>2020-02-26</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -8089,51 +8269,35 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8141,29 +8305,29 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -8186,22 +8350,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -8217,29 +8381,29 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -8255,29 +8419,29 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8293,29 +8457,29 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8331,37 +8495,33 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
@@ -8380,30 +8540,26 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -8422,34 +8578,42 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>盛祎等15名自然人</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8457,44 +8621,36 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.9%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
@@ -8503,37 +8659,33 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
@@ -8552,37 +8704,29 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
@@ -8603,32 +8747,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
@@ -8637,7 +8777,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8649,23 +8789,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
@@ -8691,32 +8831,24 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
@@ -8737,32 +8869,24 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
@@ -8783,32 +8907,28 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
           <t>2017-10-25</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
@@ -8817,7 +8937,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8839,22 +8959,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -8863,7 +8979,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8873,7 +8989,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C193" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8881,31 +9001,23 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8913,7 +9025,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8923,7 +9035,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8931,7 +9047,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -8941,21 +9057,13 @@
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
         <is>
           <t>2345.0781</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -8963,7 +9071,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8973,7 +9081,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C195" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -8981,31 +9093,23 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9013,7 +9117,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9127,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9031,31 +9139,23 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9063,7 +9163,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9073,7 +9173,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9081,31 +9185,23 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9113,7 +9209,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9219,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9131,31 +9231,23 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9163,7 +9255,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9173,7 +9265,11 @@
           <t>920116_星图测控</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
       <c r="C199" t="inlineStr">
         <is>
           <t>2024-06-30</t>
@@ -9181,31 +9277,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -9213,35 +9297,431 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
           <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 12 条</t>
-        </is>
-      </c>
-    </row>
     <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 12 条</t>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T14:44:15.938850</t>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 12 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 12 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T15:16:11.130280</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2317,11 +2317,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2341,7 +2337,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2359,7 +2355,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2379,11 +2379,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2395,7 +2399,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2417,15 +2421,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2881,15 +2881,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -2901,7 +2897,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2919,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2939,7 +2935,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2957,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2977,7 +2973,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2995,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3015,7 +3011,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3033,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3053,7 +3049,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3075,11 +3071,15 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3531,13 +3531,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3573,13 +3573,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -3615,13 +3615,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3657,13 +3657,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3699,13 +3699,13 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3779,13 +3779,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3859,15 +3859,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -3879,7 +3875,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3901,11 +3897,15 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3977,15 +3977,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -3997,7 +3993,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4019,11 +4015,15 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4387,15 +4387,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4407,7 +4403,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4471,11 +4467,15 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1153.0</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4547,11 +4547,15 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -4561,11 +4565,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4661,15 +4661,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -4679,7 +4675,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5387,14 +5387,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5403,7 +5411,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5425,20 +5433,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -5471,22 +5479,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5517,22 +5517,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -5541,7 +5533,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5563,20 +5555,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -5609,14 +5601,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5647,22 +5647,26 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5671,7 +5675,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5693,23 +5697,23 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>408.0</t>
+          <t>17952.0</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -5743,26 +5747,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5793,26 +5793,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5821,7 +5817,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5843,22 +5839,26 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5889,26 +5889,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -5917,7 +5913,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5939,22 +5935,26 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5985,30 +5985,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -6017,7 +6009,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6185,22 +6177,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6231,30 +6231,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -6263,7 +6255,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6285,20 +6277,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6331,20 +6323,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -6377,20 +6369,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6423,20 +6415,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -6469,22 +6461,30 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6515,20 +6515,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -6561,20 +6561,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8289,11 +8289,15 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -8303,11 +8307,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8327,15 +8327,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -8345,7 +8341,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -8841,11 +8841,15 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
@@ -8857,7 +8861,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8879,7 +8883,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -8917,15 +8921,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8959,20 +8959,20 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -9005,18 +9005,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
@@ -9025,7 +9029,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9047,20 +9051,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9093,20 +9097,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -9139,22 +9143,18 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9185,20 +9185,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>3825.0</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J197" t="inlineStr"/>
@@ -9231,20 +9231,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -9277,20 +9277,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -9714,7 +9714,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T16:09:12.799759</t>
+          <t>生成时间: 2026-06-12T16:30:01.235495</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -1637,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2379,15 +2379,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2399,7 +2395,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2417,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -2459,11 +2455,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2995,15 +2995,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -3037,11 +3033,15 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3531,13 +3531,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3573,15 +3573,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3593,7 +3589,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3615,13 +3611,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3657,13 +3653,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3699,11 +3695,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3737,13 +3737,13 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3779,13 +3779,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3821,15 +3821,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3841,7 +3837,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3863,11 +3859,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3977,11 +3977,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -3993,7 +3997,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4019,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4053,15 +4057,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -4387,11 +4387,15 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4403,7 +4407,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4425,15 +4429,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1153.0</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4467,13 +4467,13 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>10377.0</t>
+          <t>1153.0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -4509,11 +4509,15 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
@@ -4523,11 +4527,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -4623,15 +4623,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -4641,7 +4637,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4722,30 +4722,42 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>6999.972</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>-0.028</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4753,37 +4765,49 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2999.988</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-0.012</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4791,37 +4815,49 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1499.994</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-0.006</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4829,37 +4865,49 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4867,37 +4915,49 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>10000.0027</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10000.0</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4905,37 +4965,49 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5000.0031</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4943,37 +5015,49 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3000.0012</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>0.0012</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4981,37 +5065,49 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2912.5034</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2912.5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5019,37 +5115,49 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2015-07-09</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2000.0019</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>0.0019</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5057,75 +5165,99 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1747.5007</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1747.5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>0.0007</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.0%</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5133,37 +5265,49 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>999.9993</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-0.0007</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5171,37 +5315,49 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>339.999</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5209,29 +5365,29 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.0%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -5254,29 +5410,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5285,36 +5449,44 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5323,36 +5495,44 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
@@ -5368,22 +5548,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>688775_影石创新</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>1992-12-04</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -5406,42 +5586,38 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1992-12-04</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>盛祎等15名自然人</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5449,36 +5625,44 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.9%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5494,29 +5678,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -5525,35 +5717,47 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>920100_三协电机</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2002-11-07</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>朱绶青</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
@@ -5570,33 +5774,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5605,35 +5813,47 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>牛威</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -5643,35 +5863,47 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>吴功友</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
@@ -5681,39 +5913,47 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
@@ -5730,33 +5970,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -5765,42 +6009,42 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -5818,33 +6062,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
@@ -5853,42 +6101,42 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -5906,37 +6154,45 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>策星揽月</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -5945,44 +6201,52 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>幸福一期</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
@@ -5991,42 +6255,42 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6044,33 +6308,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -6079,42 +6347,42 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6132,37 +6400,45 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2017-10-25</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
@@ -6171,49 +6447,45 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6221,49 +6493,45 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>策星九天 (认缴→存量)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6271,49 +6539,45 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2022-12-19</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>幸福一期 (认缴→存量)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6321,42 +6585,42 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>认购数 vs 存量持股数</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>策星揽月 (认缴→存量)</t>
+          <t>上海泽升贸易有限公司 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6378,35 +6642,35 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>幸福二期 (认缴→存量)</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6428,35 +6692,35 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>策星银河 (认缴→存量)</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6478,35 +6742,35 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>920116_星图测控</t>
+          <t>603418_友升股份</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>策星逐日 (认缴→存量)</t>
+          <t>罗世兵 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6525,24 +6789,2932 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 12 条</t>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 12 条</t>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T17:00:58.890890</t>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>297.3333</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>148.6667</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>86.5984</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>603418_友升股份</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>10.1093</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>国寿疌泉</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Cheer Rise Consultants Limited</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>复星惟盈</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>苏州贤达</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>黄学英</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>史建伟</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>周金清</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>周乃鼎</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>华泰大健康一号</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>高新同华</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>陆民</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>688758_赛分科技</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>黄学英/刘鸿雁</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>深圳中证投资有限责任公司</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>厦门富凯海创投资管理有限责任公司</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>QM101 Limited</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>EARN ACE LIMITED</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>香港迅雷有限公司</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2023-03-24</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>北京岚锋创视网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>盛祎等15名自然人</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>price×shares vs amount diff=0.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>盛祎</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2002-11-07</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>朱绶青</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>四方股份</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>吴功友(王金林代持)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2016-12-14</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>牛威(罗永红代持)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>策星九天</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>幸福二期</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>策星逐日</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>吴功友</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>幸福一期</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>策星揽月</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2017-10-25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>策星九天 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>幸福一期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>策星揽月 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>幸福二期 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>策星银河 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>策星逐日 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>认购数 vs 存量持股数</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 12 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 12 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生成时间: 2026-06-12T17:05:42.776363</t>
         </is>
       </c>
     </row>
